--- a/docs/order_2.xlsx
+++ b/docs/order_2.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Order" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,6 +44,156 @@
     <t>Manufacturer Product Number</t>
   </si>
   <si>
+    <t>RNCF0603TKY49R9</t>
+  </si>
+  <si>
+    <t>RNCF0603TKY1K00</t>
+  </si>
+  <si>
+    <t>RNCF0603TKY499R</t>
+  </si>
+  <si>
+    <t>RG2012N-510-W-T1</t>
+  </si>
+  <si>
+    <t>ERA-3ARW104V</t>
+  </si>
+  <si>
+    <t>RG1608N-103-W-T5</t>
+  </si>
+  <si>
+    <t>RG1608N-470-W-T1</t>
+  </si>
+  <si>
+    <t>RNCF0603AKT10R0</t>
+  </si>
+  <si>
+    <t>GRM1885C1H1R0WA01D</t>
+  </si>
+  <si>
+    <t>AD8066ARZ-R7</t>
+  </si>
+  <si>
+    <t>ADP2303ARDZ-5.0-R7</t>
+  </si>
+  <si>
+    <t>ADP7118AUJZ-3.3-R7</t>
+  </si>
+  <si>
+    <t>KGM15ACG1H102FT</t>
+  </si>
+  <si>
+    <t>RN73R1JTTD22R0B25</t>
+  </si>
+  <si>
+    <t>GCM1885C2A561FA16D</t>
+  </si>
+  <si>
+    <t>C0603C161F5GACTU</t>
+  </si>
+  <si>
+    <t>CC0603FRNPO9BN390</t>
+  </si>
+  <si>
+    <t>C0603C681F5GACTU</t>
+  </si>
+  <si>
+    <t>MLF1608A1R0JT000</t>
+  </si>
+  <si>
+    <t>MLF1608A1R5JT000</t>
+  </si>
+  <si>
+    <t>MLF1608A1R8JT000</t>
+  </si>
+  <si>
+    <t>CC0603FRNPO9BN201</t>
+  </si>
+  <si>
+    <t>C0603C391F5GACTU</t>
+  </si>
+  <si>
+    <t>CL10C100CB8NNNC</t>
+  </si>
+  <si>
+    <t>GQM1875C2E120GB12D</t>
+  </si>
+  <si>
+    <t>C0603C121F5GACTU</t>
+  </si>
+  <si>
+    <t>CC0603FRNPO9BN820</t>
+  </si>
+  <si>
+    <t>KGM15ACG1H221FT</t>
+  </si>
+  <si>
+    <t>C0805C473J3GACTU</t>
+  </si>
+  <si>
+    <t>RNCF0603TKY100R</t>
+  </si>
+  <si>
+    <t>QSCP251Q1R0A1GV001T</t>
+  </si>
+  <si>
+    <t>GRT1885C1E103FA02D</t>
+  </si>
+  <si>
+    <t>ERA-3ARW202V</t>
+  </si>
+  <si>
+    <t>ERA-3AEB52R3V</t>
+  </si>
+  <si>
+    <t>GCM31C5C1H104FA16L</t>
+  </si>
+  <si>
+    <t>RMCF0805FT60K4</t>
+  </si>
+  <si>
+    <t>RC0805FR-0724K3L</t>
+  </si>
+  <si>
+    <t>RMCF0805FT150K</t>
+  </si>
+  <si>
+    <t>CL10A225KO8NNNC</t>
+  </si>
+  <si>
+    <t>GRM21BR61C106KE15L</t>
+  </si>
+  <si>
+    <t>399-C0603C223K5RACTUCT-ND</t>
+  </si>
+  <si>
+    <t>GRM31CR60J476KE19L</t>
+  </si>
+  <si>
+    <t>SMBJ12A-E3/52</t>
+  </si>
+  <si>
+    <t>SMBJ8.5A</t>
+  </si>
+  <si>
+    <t>SK54A-LTP</t>
+  </si>
+  <si>
+    <t>SK34A-LTP</t>
+  </si>
+  <si>
+    <t>SRR1260-4R7Y</t>
+  </si>
+  <si>
+    <t>DFE322520FD-4R7M=P2</t>
+  </si>
+  <si>
+    <t>NRS5030T6R8MMGJ</t>
+  </si>
+  <si>
+    <t>AD8130ARMZ-REEL7</t>
+  </si>
+  <si>
     <t>SFH 4253-R</t>
   </si>
   <si>
@@ -98,9 +248,6 @@
     <t>CL10B104JB8NNNC</t>
   </si>
   <si>
-    <t>GRM21BR61C106KE15L</t>
-  </si>
-  <si>
     <t>CC0603JRX7R7BB105</t>
   </si>
   <si>
@@ -198,160 +345,13 @@
   </si>
   <si>
     <t>RMCF0603FT27K4</t>
-  </si>
-  <si>
-    <t>RNCF0603TKY49R9</t>
-  </si>
-  <si>
-    <t>RNCF0603TKY1K00</t>
-  </si>
-  <si>
-    <t>RNCF0603TKY499R</t>
-  </si>
-  <si>
-    <t>RG2012N-510-W-T1</t>
-  </si>
-  <si>
-    <t>ERA-3ARW104V</t>
-  </si>
-  <si>
-    <t>RG1608N-103-W-T5</t>
-  </si>
-  <si>
-    <t>RG1608N-470-W-T1</t>
-  </si>
-  <si>
-    <t>RNCF0603AKT10R0</t>
-  </si>
-  <si>
-    <t>GRM1885C1H1R0WA01D</t>
-  </si>
-  <si>
-    <t>AD8066ARZ-R7</t>
-  </si>
-  <si>
-    <t>ADP2303ARDZ-5.0-R7</t>
-  </si>
-  <si>
-    <t>ADP7118AUJZ-3.3-R7</t>
-  </si>
-  <si>
-    <t>KGM15ACG1H102FT</t>
-  </si>
-  <si>
-    <t>RN73R1JTTD22R0B25</t>
-  </si>
-  <si>
-    <t>GCM1885C2A561FA16D</t>
-  </si>
-  <si>
-    <t>C0603C161F5GACTU</t>
-  </si>
-  <si>
-    <t>CC0603FRNPO9BN390</t>
-  </si>
-  <si>
-    <t>C0603C681F5GACTU</t>
-  </si>
-  <si>
-    <t>MLF1608A1R0JT000</t>
-  </si>
-  <si>
-    <t>MLF1608A1R5JT000</t>
-  </si>
-  <si>
-    <t>MLF1608A1R8JT000</t>
-  </si>
-  <si>
-    <t>CC0603FRNPO9BN201</t>
-  </si>
-  <si>
-    <t>C0603C391F5GACTU</t>
-  </si>
-  <si>
-    <t>CL10C100CB8NNNC</t>
-  </si>
-  <si>
-    <t>GQM1875C2E120GB12D</t>
-  </si>
-  <si>
-    <t>C0603C121F5GACTU</t>
-  </si>
-  <si>
-    <t>CC0603FRNPO9BN820</t>
-  </si>
-  <si>
-    <t>KGM15ACG1H221FT</t>
-  </si>
-  <si>
-    <t>C0805C473J3GACTU</t>
-  </si>
-  <si>
-    <t>RNCF0603TKY100R</t>
-  </si>
-  <si>
-    <t>QSCP251Q1R0A1GV001T</t>
-  </si>
-  <si>
-    <t>GRT1885C1E103FA02D</t>
-  </si>
-  <si>
-    <t>ERA-3ARW202V</t>
-  </si>
-  <si>
-    <t>ERA-3AEB52R3V</t>
-  </si>
-  <si>
-    <t>GCM31C5C1H104FA16L</t>
-  </si>
-  <si>
-    <t>RMCF0805FT60K4</t>
-  </si>
-  <si>
-    <t>RC0805FR-0724K3L</t>
-  </si>
-  <si>
-    <t>RMCF0805FT150K</t>
-  </si>
-  <si>
-    <t>CL10A225KO8NNNC</t>
-  </si>
-  <si>
-    <t>399-C0603C223K5RACTUCT-ND</t>
-  </si>
-  <si>
-    <t>GRM31CR60J476KE19L</t>
-  </si>
-  <si>
-    <t>SMBJ12A-E3/52</t>
-  </si>
-  <si>
-    <t>SMBJ8.5A</t>
-  </si>
-  <si>
-    <t>SK54A-LTP</t>
-  </si>
-  <si>
-    <t>SK34A-LTP</t>
-  </si>
-  <si>
-    <t>SRR1260-4R7Y</t>
-  </si>
-  <si>
-    <t>DFE322520FD-4R7M=P2</t>
-  </si>
-  <si>
-    <t>NRS5030T6R8MMGJ</t>
-  </si>
-  <si>
-    <t>AD8130ARMZ-REEL7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -663,12 +663,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A653A91-A063-4641-87A1-3F78AB4F678A}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -676,852 +676,852 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49">
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50">
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51">
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52">
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53">
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54">
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55">
         <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56">
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57">
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58">
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59">
         <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60">
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61">
         <v>20</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62">
         <v>50</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63">
         <v>50</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64">
         <v>50</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65">
         <v>50</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>50</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67">
         <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68">
         <v>50</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69">
         <v>50</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70">
         <v>50</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71">
         <v>50</v>
       </c>
       <c r="B71" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72">
         <v>50</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73">
         <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74">
         <v>20</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75">
         <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76">
         <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77">
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78">
         <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79">
         <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80">
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81">
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82">
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83">
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84">
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85">
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86">
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87">
         <v>3</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88">
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89">
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90">
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91">
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92">
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93">
         <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
       <c r="A94">
         <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95">
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96">
         <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97">
         <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98">
         <v>10</v>
       </c>
       <c r="B98" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
       <c r="A99">
         <v>10</v>
       </c>
       <c r="B99" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100">
         <v>10</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101">
         <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
       <c r="A102">
         <v>3</v>
       </c>
       <c r="B102" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
       <c r="A103">
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104">
         <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
       <c r="A105">
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
       <c r="A106">
         <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
       <c r="A107">
         <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
